--- a/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP155"/>
+  <dimension ref="A1:BP156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3530,7 +3530,7 @@
         <v>2.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.36</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.27</v>
@@ -6800,7 +6800,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR29" t="n">
         <v>2.89</v>
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ39" t="n">
         <v>2.18</v>
@@ -10070,7 +10070,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR44" t="n">
         <v>1.23</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -13558,7 +13558,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR60" t="n">
         <v>1.21</v>
@@ -14863,7 +14863,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ66" t="n">
         <v>2</v>
@@ -17046,7 +17046,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR76" t="n">
         <v>1.1</v>
@@ -17697,7 +17697,7 @@
         <v>0.2</v>
       </c>
       <c r="AP79" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.18</v>
@@ -19444,7 +19444,7 @@
         <v>1</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR87" t="n">
         <v>1.3</v>
@@ -20967,7 +20967,7 @@
         <v>0.57</v>
       </c>
       <c r="AP94" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.45</v>
@@ -23368,7 +23368,7 @@
         <v>0.91</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR105" t="n">
         <v>1.05</v>
@@ -23583,7 +23583,7 @@
         <v>0.71</v>
       </c>
       <c r="AP106" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.91</v>
@@ -25984,7 +25984,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR117" t="n">
         <v>0.82</v>
@@ -27074,7 +27074,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR122" t="n">
         <v>1.54</v>
@@ -29905,7 +29905,7 @@
         <v>1.22</v>
       </c>
       <c r="AP135" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.55</v>
@@ -30344,7 +30344,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR137" t="n">
         <v>1.08</v>
@@ -31649,7 +31649,7 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AQ143" t="n">
         <v>1</v>
@@ -33832,7 +33832,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ153" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AR153" t="n">
         <v>1.83</v>
@@ -34344,6 +34344,224 @@
       </c>
       <c r="BP155" t="n">
         <v>1.14</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>8280499</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>46081.625</v>
+      </c>
+      <c r="F156" t="n">
+        <v>23</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Levadiakos</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>1</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>1</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="n">
+        <v>1</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>['13']</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R156" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S156" t="n">
+        <v>3</v>
+      </c>
+      <c r="T156" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U156" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="V156" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="W156" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X156" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF156" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BI156" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BJ156" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK156" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="BL156" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BM156" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BN156" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BO156" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="BP156" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP156"/>
+  <dimension ref="A1:BP160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.91</v>
@@ -2219,10 +2219,10 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ9" t="n">
         <v>1</v>
@@ -3094,7 +3094,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR12" t="n">
         <v>2.7</v>
@@ -3309,7 +3309,7 @@
         <v>3</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.55</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.33</v>
@@ -3966,7 +3966,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
@@ -4838,7 +4838,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR20" t="n">
         <v>1.51</v>
@@ -5274,7 +5274,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR22" t="n">
         <v>1.07</v>
@@ -5489,7 +5489,7 @@
         <v>1.5</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.55</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR24" t="n">
         <v>1.02</v>
@@ -5925,7 +5925,7 @@
         <v>3</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ25" t="n">
         <v>1</v>
@@ -6146,7 +6146,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR26" t="n">
         <v>1.44</v>
@@ -6579,10 +6579,10 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR28" t="n">
         <v>1.76</v>
@@ -8323,10 +8323,10 @@
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR36" t="n">
         <v>1.32</v>
@@ -8544,7 +8544,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR37" t="n">
         <v>0.82</v>
@@ -8980,7 +8980,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ39" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR39" t="n">
         <v>0.87</v>
@@ -9413,10 +9413,10 @@
         <v>2</v>
       </c>
       <c r="AP41" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ41" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR41" t="n">
         <v>2.54</v>
@@ -9631,7 +9631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.55</v>
@@ -9852,7 +9852,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR43" t="n">
         <v>1.44</v>
@@ -10721,7 +10721,7 @@
         <v>0.33</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ47" t="n">
         <v>0.18</v>
@@ -11593,7 +11593,7 @@
         <v>0.67</v>
       </c>
       <c r="AP51" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ51" t="n">
         <v>0.91</v>
@@ -12032,7 +12032,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ53" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR53" t="n">
         <v>1.77</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR54" t="n">
         <v>1.65</v>
@@ -12465,7 +12465,7 @@
         <v>1.5</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ55" t="n">
         <v>1</v>
@@ -12686,7 +12686,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR56" t="n">
         <v>2.61</v>
@@ -12901,7 +12901,7 @@
         <v>1.33</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ57" t="n">
         <v>1.36</v>
@@ -13340,7 +13340,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR59" t="n">
         <v>2.31</v>
@@ -13773,7 +13773,7 @@
         <v>2.33</v>
       </c>
       <c r="AP61" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ61" t="n">
         <v>1.8</v>
@@ -14648,7 +14648,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR65" t="n">
         <v>1.86</v>
@@ -14866,7 +14866,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ66" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR66" t="n">
         <v>1.2</v>
@@ -15302,7 +15302,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ68" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR68" t="n">
         <v>1.07</v>
@@ -15735,7 +15735,7 @@
         <v>2.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.8</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ73" t="n">
         <v>1.36</v>
@@ -16607,7 +16607,7 @@
         <v>1.6</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ74" t="n">
         <v>1</v>
@@ -16828,7 +16828,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR75" t="n">
         <v>1.87</v>
@@ -17043,7 +17043,7 @@
         <v>1.25</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ76" t="n">
         <v>1.33</v>
@@ -18136,7 +18136,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ81" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR81" t="n">
         <v>0.97</v>
@@ -18354,7 +18354,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR82" t="n">
         <v>1.47</v>
@@ -18787,10 +18787,10 @@
         <v>2</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ84" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR84" t="n">
         <v>1.54</v>
@@ -19223,7 +19223,7 @@
         <v>1.33</v>
       </c>
       <c r="AP86" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ86" t="n">
         <v>1</v>
@@ -19877,10 +19877,10 @@
         <v>1.17</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR89" t="n">
         <v>2.01</v>
@@ -20313,7 +20313,7 @@
         <v>1</v>
       </c>
       <c r="AP91" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ91" t="n">
         <v>1</v>
@@ -20970,7 +20970,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR94" t="n">
         <v>1.29</v>
@@ -21188,7 +21188,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ95" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR95" t="n">
         <v>0.9399999999999999</v>
@@ -21624,7 +21624,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ97" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR97" t="n">
         <v>1.69</v>
@@ -21839,7 +21839,7 @@
         <v>1.71</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ98" t="n">
         <v>1</v>
@@ -22060,7 +22060,7 @@
         <v>1</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR99" t="n">
         <v>1.21</v>
@@ -22275,7 +22275,7 @@
         <v>1.29</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ100" t="n">
         <v>1</v>
@@ -22929,7 +22929,7 @@
         <v>1.33</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.36</v>
@@ -23365,7 +23365,7 @@
         <v>1.5</v>
       </c>
       <c r="AP105" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ105" t="n">
         <v>1.33</v>
@@ -24022,7 +24022,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ108" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR108" t="n">
         <v>1.35</v>
@@ -24458,7 +24458,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR110" t="n">
         <v>0.91</v>
@@ -24676,7 +24676,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ111" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR111" t="n">
         <v>1.59</v>
@@ -24891,7 +24891,7 @@
         <v>0.14</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.18</v>
@@ -25109,7 +25109,7 @@
         <v>1.25</v>
       </c>
       <c r="AP113" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ113" t="n">
         <v>1</v>
@@ -25330,7 +25330,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ114" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR114" t="n">
         <v>1.26</v>
@@ -25545,7 +25545,7 @@
         <v>0.86</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ115" t="n">
         <v>1</v>
@@ -26199,7 +26199,7 @@
         <v>1</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.55</v>
@@ -26638,7 +26638,7 @@
         <v>1</v>
       </c>
       <c r="AQ120" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR120" t="n">
         <v>1.18</v>
@@ -27728,7 +27728,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR125" t="n">
         <v>0.92</v>
@@ -28161,7 +28161,7 @@
         <v>0.75</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.91</v>
@@ -28382,7 +28382,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR128" t="n">
         <v>1.72</v>
@@ -28597,7 +28597,7 @@
         <v>1.11</v>
       </c>
       <c r="AP129" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ129" t="n">
         <v>1</v>
@@ -28815,7 +28815,7 @@
         <v>0.11</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.18</v>
@@ -29036,7 +29036,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ131" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR131" t="n">
         <v>1.91</v>
@@ -29254,7 +29254,7 @@
         <v>1</v>
       </c>
       <c r="AQ132" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR132" t="n">
         <v>1.23</v>
@@ -30123,10 +30123,10 @@
         <v>2.22</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ136" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR136" t="n">
         <v>1.15</v>
@@ -30998,7 +30998,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ140" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AR140" t="n">
         <v>0.87</v>
@@ -31216,7 +31216,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ141" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="AR141" t="n">
         <v>1.65</v>
@@ -31431,10 +31431,10 @@
         <v>1.3</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AQ142" t="n">
-        <v>1.27</v>
+        <v>1.17</v>
       </c>
       <c r="AR142" t="n">
         <v>1.23</v>
@@ -31867,10 +31867,10 @@
         <v>2.3</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AQ144" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AR144" t="n">
         <v>1.95</v>
@@ -32085,7 +32085,7 @@
         <v>1</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.91</v>
@@ -32957,7 +32957,7 @@
         <v>1.09</v>
       </c>
       <c r="AP149" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AQ149" t="n">
         <v>1</v>
@@ -34501,13 +34501,13 @@
         <v>2</v>
       </c>
       <c r="AV156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW156" t="n">
         <v>7</v>
       </c>
       <c r="AX156" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY156" t="n">
         <v>9</v>
@@ -34562,6 +34562,878 @@
       </c>
       <c r="BP156" t="n">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>8280576</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>46082.45833333334</v>
+      </c>
+      <c r="F157" t="n">
+        <v>23</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Panserraikos</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Olympiakos Piraeus</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>1</v>
+      </c>
+      <c r="M157" t="n">
+        <v>2</v>
+      </c>
+      <c r="N157" t="n">
+        <v>3</v>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>['60', '70']</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>12</v>
+      </c>
+      <c r="R157" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S157" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T157" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U157" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V157" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="W157" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="X157" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y157" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z157" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA157" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AB157" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC157" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD157" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="AE157" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF157" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH157" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AI157" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AJ157" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK157" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AL157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM157" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AN157" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP157" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ157" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ157" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA157" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB157" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC157" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD157" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="BE157" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BF157" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BG157" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH157" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BI157" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ157" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK157" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BL157" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BM157" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="BN157" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BO157" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BP157" t="n">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>8280560</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>46082.52083333334</v>
+      </c>
+      <c r="F158" t="n">
+        <v>23</v>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Volos NFC</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>1</v>
+      </c>
+      <c r="J158" t="n">
+        <v>1</v>
+      </c>
+      <c r="K158" t="n">
+        <v>2</v>
+      </c>
+      <c r="L158" t="n">
+        <v>2</v>
+      </c>
+      <c r="M158" t="n">
+        <v>2</v>
+      </c>
+      <c r="N158" t="n">
+        <v>4</v>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>['14', '61']</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>['34', '90+8']</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R158" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="T158" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U158" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V158" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W158" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X158" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ158" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA158" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB158" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC158" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD158" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE158" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF158" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BG158" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BH158" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BI158" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BJ158" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BK158" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BL158" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BM158" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BN158" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO158" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BP158" t="n">
+        <v>1.19</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>8280544</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>46082.58333333334</v>
+      </c>
+      <c r="F159" t="n">
+        <v>23</v>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>Asteras Tripolis</t>
+        </is>
+      </c>
+      <c r="I159" t="n">
+        <v>1</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" t="n">
+        <v>2</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="n">
+        <v>2</v>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>['7', '89']</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R159" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S159" t="n">
+        <v>8</v>
+      </c>
+      <c r="T159" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="U159" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="V159" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="W159" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X159" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ159" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA159" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB159" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC159" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD159" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BE159" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BF159" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG159" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH159" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI159" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BJ159" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BK159" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BL159" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM159" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BN159" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO159" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="BP159" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>8280512</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>46082.625</v>
+      </c>
+      <c r="F160" t="n">
+        <v>23</v>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>1</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1</v>
+      </c>
+      <c r="L160" t="n">
+        <v>3</v>
+      </c>
+      <c r="M160" t="n">
+        <v>1</v>
+      </c>
+      <c r="N160" t="n">
+        <v>4</v>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>['9', '65', '80']</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>['72']</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="R160" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S160" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T160" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="U160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V160" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="W160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X160" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ160" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA160" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB160" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC160" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD160" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BE160" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF160" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG160" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BH160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BI160" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BJ160" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BK160" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BL160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BM160" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BN160" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BO160" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="BP160" t="n">
+        <v>1.21</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP160"/>
+  <dimension ref="A1:BP162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,7 +2440,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14" t="n">
         <v>1.33</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19" t="n">
         <v>1.36</v>
@@ -5056,7 +5056,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
@@ -5271,7 +5271,7 @@
         <v>3</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ22" t="n">
         <v>1.17</v>
@@ -6364,7 +6364,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR27" t="n">
         <v>1.42</v>
@@ -6579,7 +6579,7 @@
         <v>3</v>
       </c>
       <c r="AP28" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ28" t="n">
         <v>2.08</v>
@@ -7672,7 +7672,7 @@
         <v>1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR33" t="n">
         <v>1.1</v>
@@ -8977,7 +8977,7 @@
         <v>2</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ39" t="n">
         <v>2.08</v>
@@ -9631,7 +9631,7 @@
         <v>1.33</v>
       </c>
       <c r="AP42" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ42" t="n">
         <v>1.55</v>
@@ -10288,7 +10288,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR45" t="n">
         <v>0.84</v>
@@ -11160,7 +11160,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR49" t="n">
         <v>1.96</v>
@@ -11375,7 +11375,7 @@
         <v>1.33</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ50" t="n">
         <v>1</v>
@@ -12247,7 +12247,7 @@
         <v>0</v>
       </c>
       <c r="AP54" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.42</v>
@@ -13776,7 +13776,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR61" t="n">
         <v>1.12</v>
@@ -14212,7 +14212,7 @@
         <v>1</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR63" t="n">
         <v>1.09</v>
@@ -14863,7 +14863,7 @@
         <v>1.75</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ66" t="n">
         <v>2.08</v>
@@ -15735,10 +15735,10 @@
         <v>2.5</v>
       </c>
       <c r="AP70" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR70" t="n">
         <v>1.72</v>
@@ -17264,7 +17264,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ77" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR77" t="n">
         <v>1.29</v>
@@ -17697,7 +17697,7 @@
         <v>0.2</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ79" t="n">
         <v>0.18</v>
@@ -18572,7 +18572,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR83" t="n">
         <v>1.78</v>
@@ -18787,7 +18787,7 @@
         <v>2</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ84" t="n">
         <v>2.08</v>
@@ -19008,7 +19008,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR85" t="n">
         <v>2.23</v>
@@ -20967,7 +20967,7 @@
         <v>0.57</v>
       </c>
       <c r="AP94" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ94" t="n">
         <v>0.42</v>
@@ -21406,7 +21406,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR96" t="n">
         <v>1.44</v>
@@ -21839,7 +21839,7 @@
         <v>1.71</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ98" t="n">
         <v>1</v>
@@ -23150,7 +23150,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR104" t="n">
         <v>2.02</v>
@@ -23583,7 +23583,7 @@
         <v>0.71</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.91</v>
@@ -23804,7 +23804,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR107" t="n">
         <v>0.88</v>
@@ -24891,7 +24891,7 @@
         <v>0.14</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ112" t="n">
         <v>0.18</v>
@@ -25548,7 +25548,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR115" t="n">
         <v>2.02</v>
@@ -27946,7 +27946,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ126" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR126" t="n">
         <v>1.25</v>
@@ -28597,7 +28597,7 @@
         <v>1.11</v>
       </c>
       <c r="AP129" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ129" t="n">
         <v>1</v>
@@ -29905,7 +29905,7 @@
         <v>1.22</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ135" t="n">
         <v>1.55</v>
@@ -30562,7 +30562,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ138" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR138" t="n">
         <v>1.58</v>
@@ -31649,10 +31649,10 @@
         <v>1</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AR143" t="n">
         <v>1.49</v>
@@ -32085,7 +32085,7 @@
         <v>1</v>
       </c>
       <c r="AP145" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ145" t="n">
         <v>0.91</v>
@@ -33396,7 +33396,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AR151" t="n">
         <v>1.31</v>
@@ -34483,7 +34483,7 @@
         <v>1.45</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AQ156" t="n">
         <v>1.33</v>
@@ -35355,7 +35355,7 @@
         <v>1.27</v>
       </c>
       <c r="AP160" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AQ160" t="n">
         <v>1.17</v>
@@ -35434,6 +35434,442 @@
       </c>
       <c r="BP160" t="n">
         <v>1.21</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>8280584</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>46085.54166666666</v>
+      </c>
+      <c r="F161" t="n">
+        <v>1</v>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>OFI</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>2</v>
+      </c>
+      <c r="J161" t="n">
+        <v>1</v>
+      </c>
+      <c r="K161" t="n">
+        <v>3</v>
+      </c>
+      <c r="L161" t="n">
+        <v>4</v>
+      </c>
+      <c r="M161" t="n">
+        <v>1</v>
+      </c>
+      <c r="N161" t="n">
+        <v>5</v>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>['7', '15', '51', '86']</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>['45+1']</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R161" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="S161" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="T161" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U161" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="V161" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="W161" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X161" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ161" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB161" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD161" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="BE161" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="BF161" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG161" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BH161" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BI161" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BJ161" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BK161" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BL161" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BM161" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BN161" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BO161" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BP161" t="n">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>8280500</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>46085.625</v>
+      </c>
+      <c r="F162" t="n">
+        <v>18</v>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>1</v>
+      </c>
+      <c r="K162" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" t="n">
+        <v>1</v>
+      </c>
+      <c r="M162" t="n">
+        <v>4</v>
+      </c>
+      <c r="N162" t="n">
+        <v>5</v>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>['32', '72', '88', '90+2']</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>6</v>
+      </c>
+      <c r="R162" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S162" t="n">
+        <v>2</v>
+      </c>
+      <c r="T162" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="W162" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X162" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ162" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA162" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB162" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC162" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD162" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="BE162" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF162" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BG162" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BH162" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BI162" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ162" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BK162" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BL162" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BM162" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BN162" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BO162" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="BP162" t="n">
+        <v>1.19</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Greece Super League_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP162"/>
+  <dimension ref="A1:BP164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,7 +1129,7 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3" t="n">
         <v>1</v>
@@ -1350,7 +1350,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ5" t="n">
         <v>0.18</v>
@@ -1786,7 +1786,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ10" t="n">
         <v>1</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.42</v>
@@ -3312,7 +3312,7 @@
         <v>2.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR13" t="n">
         <v>2.22</v>
@@ -4402,7 +4402,7 @@
         <v>1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR18" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR23" t="n">
         <v>1.27</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.18</v>
@@ -7233,7 +7233,7 @@
         <v>1.5</v>
       </c>
       <c r="AP31" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ31" t="n">
         <v>1</v>
@@ -8108,7 +8108,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR35" t="n">
         <v>0.93</v>
@@ -9634,7 +9634,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR42" t="n">
         <v>1.28</v>
@@ -10939,7 +10939,7 @@
         <v>1.5</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48" t="n">
         <v>1.36</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.91</v>
@@ -11596,7 +11596,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR51" t="n">
         <v>1.2</v>
@@ -11814,7 +11814,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR52" t="n">
         <v>0.92</v>
@@ -13991,7 +13991,7 @@
         <v>1.25</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ62" t="n">
         <v>1</v>
@@ -14430,7 +14430,7 @@
         <v>0.82</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR64" t="n">
         <v>0.92</v>
@@ -14645,7 +14645,7 @@
         <v>0</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ65" t="n">
         <v>0.42</v>
@@ -16174,7 +16174,7 @@
         <v>2.55</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR72" t="n">
         <v>2.15</v>
@@ -16825,7 +16825,7 @@
         <v>1.4</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ75" t="n">
         <v>1.17</v>
@@ -17915,10 +17915,10 @@
         <v>1</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR80" t="n">
         <v>1.62</v>
@@ -20095,10 +20095,10 @@
         <v>1.17</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR90" t="n">
         <v>2</v>
@@ -20534,7 +20534,7 @@
         <v>2.09</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR92" t="n">
         <v>1.71</v>
@@ -21621,7 +21621,7 @@
         <v>2.17</v>
       </c>
       <c r="AP97" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ97" t="n">
         <v>2.08</v>
@@ -22714,7 +22714,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR102" t="n">
         <v>1.34</v>
@@ -23147,7 +23147,7 @@
         <v>1</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ104" t="n">
         <v>0.91</v>
@@ -23586,7 +23586,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR106" t="n">
         <v>1.42</v>
@@ -24673,7 +24673,7 @@
         <v>2.29</v>
       </c>
       <c r="AP111" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ111" t="n">
         <v>2.08</v>
@@ -25763,7 +25763,7 @@
         <v>1.14</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.36</v>
@@ -26202,7 +26202,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR118" t="n">
         <v>1.33</v>
@@ -27071,7 +27071,7 @@
         <v>1.88</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.33</v>
@@ -28164,7 +28164,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR127" t="n">
         <v>1.25</v>
@@ -29033,7 +29033,7 @@
         <v>2.13</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ131" t="n">
         <v>2.08</v>
@@ -29908,7 +29908,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR135" t="n">
         <v>1.53</v>
@@ -30559,7 +30559,7 @@
         <v>2</v>
       </c>
       <c r="AP138" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ138" t="n">
         <v>1.91</v>
@@ -32088,7 +32088,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ145" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR145" t="n">
         <v>1.64</v>
@@ -32742,7 +32742,7 @@
         <v>1</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AR148" t="n">
         <v>1.15</v>
@@ -33611,7 +33611,7 @@
         <v>1</v>
       </c>
       <c r="AP152" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AQ152" t="n">
         <v>1</v>
@@ -33829,7 +33829,7 @@
         <v>1.6</v>
       </c>
       <c r="AP153" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.33</v>
@@ -34050,7 +34050,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ154" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR154" t="n">
         <v>1.05</v>
@@ -35870,6 +35870,442 @@
       </c>
       <c r="BP162" t="n">
         <v>1.19</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>8280577</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>46088.5</v>
+      </c>
+      <c r="F163" t="n">
+        <v>24</v>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R163" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T163" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="U163" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V163" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="W163" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X163" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ163" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA163" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB163" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC163" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD163" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BE163" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BF163" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BG163" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BH163" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BI163" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BJ163" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BK163" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BM163" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BN163" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BO163" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BP163" t="n">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>8280527</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Greece Super League</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>46088.54166666666</v>
+      </c>
+      <c r="F164" t="n">
+        <v>24</v>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>1</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" t="n">
+        <v>1</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="n">
+        <v>1</v>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>['5']</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R164" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S164" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="T164" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U164" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="V164" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="W164" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X164" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ164" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA164" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB164" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC164" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD164" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BE164" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF164" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG164" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BH164" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BI164" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ164" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BK164" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BL164" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BM164" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BN164" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO164" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="BP164" t="n">
+        <v>1.17</v>
       </c>
     </row>
   </sheetData>
